--- a/qL.xlsx
+++ b/qL.xlsx
@@ -1,24 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Howley_Bradford_Streams\Howley_Bradford_Streams\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E735C76-5227-4785-8188-DFF827BB27F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A58260B2-4D70-45C2-8F93-C9254C470525}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
     <sheet name="6" sheetId="2" r:id="rId2"/>
     <sheet name="5" sheetId="3" r:id="rId3"/>
-    <sheet name="9" sheetId="4" r:id="rId4"/>
-    <sheet name="TransportModel" sheetId="5" r:id="rId5"/>
-    <sheet name="Sheet2" sheetId="7" r:id="rId6"/>
+    <sheet name="Sheet1" sheetId="8" r:id="rId4"/>
+    <sheet name="9" sheetId="4" r:id="rId5"/>
+    <sheet name="TransportModel" sheetId="5" r:id="rId6"/>
+    <sheet name="Sheet2" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="74">
   <si>
     <t>Date</t>
   </si>
@@ -242,6 +243,24 @@
   </si>
   <si>
     <t xml:space="preserve">distance (km) </t>
+  </si>
+  <si>
+    <t>cum_pixel_diff</t>
+  </si>
+  <si>
+    <t>frac_discharge</t>
+  </si>
+  <si>
+    <t>pixel</t>
+  </si>
+  <si>
+    <t>cum_distance</t>
+  </si>
+  <si>
+    <t>frac_Q</t>
+  </si>
+  <si>
+    <t>cum_pixel_difference</t>
   </si>
 </sst>
 </file>
@@ -774,6 +793,747 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$B$2:$B$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1267.3699999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2467.91</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4497.8599999999997</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6130.37</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$D$2:$D$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="1">
+                  <c:v>0.18409103680809216</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.42402922169148638</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.89815453779151444</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.9922239393087946</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-46E1-4223-8261-B351E557E158}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1063418767"/>
+        <c:axId val="1063402447"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1063418767"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1063402447"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1063402447"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1063418767"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>12/12/2025</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'9'!$M$9:$M$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.15918655185298042</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.7513476994329094</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.782632927087664</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5.2363819182292328</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'9'!$N$9:$N$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="1">
+                  <c:v>4.0599999999999996</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.7</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3.04</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.54</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-4FB9-4776-BEAA-B9FA9E002D5D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="136937984"/>
+        <c:axId val="136938464"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="136937984"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="136938464"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="136938464"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="136937984"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
       <c:tx>
         <c:rich>
           <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
@@ -918,19 +1678,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>37.743591811441398</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>36.61132775918442</c:v>
+                  <c:v>1.1322640522569827</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>11.06096003041203</c:v>
+                  <c:v>26.682631781029372</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.7256218545114974</c:v>
+                  <c:v>34.017969956929903</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.49819048272095157</c:v>
+                  <c:v>37.245401328720448</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1153,7 +1913,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -1299,31 +2059,31 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>'9'!$S$9:$S$13</c:f>
+              <c:f>'9'!$T$9:$T$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>68.679981822201199</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>66.61966188986851</c:v>
+                  <c:v>2.0603199323326855</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>20.127033421194184</c:v>
+                  <c:v>48.552948401007015</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6.7793134930703749</c:v>
+                  <c:v>61.900668329130831</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.90653039774811839</c:v>
+                  <c:v>67.773451424453086</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'9'!$T$9:$T$13</c:f>
+              <c:f>'9'!$U$9:$U$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
@@ -1536,7 +2296,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart14.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -1695,19 +2455,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>100.03049449091</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>97.029695478262397</c:v>
+                  <c:v>3.0007990126476041</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>29.314467656226288</c:v>
+                  <c:v>70.716026834683717</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>9.873882651516892</c:v>
+                  <c:v>90.156611839393108</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.3203364583371593</c:v>
+                  <c:v>98.710158032572849</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1924,7 +2684,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart15.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -2015,8 +2775,8 @@
             <c:trendlineLbl>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="-7.8005249343832024E-3"/>
-                  <c:y val="-0.48507108486439193"/>
+                  <c:x val="-7.3407699037620301E-3"/>
+                  <c:y val="-0.15782407407407406"/>
                 </c:manualLayout>
               </c:layout>
               <c:numFmt formatCode="General" sourceLinked="0"/>
@@ -2051,23 +2811,20 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>'9'!$Q$2:$Q$6</c:f>
+              <c:f>'9'!$Q$3:$Q$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>904.88</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>904.88</c:v>
+                  <c:v>2002.8</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2002.8</c:v>
+                  <c:v>3140.96</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3140.96</c:v>
-                </c:pt>
-                <c:pt idx="4">
                   <c:v>8475.9599999999991</c:v>
                 </c:pt>
               </c:numCache>
@@ -2075,24 +2832,18 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'9'!$R$2:$R$6</c:f>
+              <c:f>'9'!$S$4:$S$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>0.70694468916286168</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.97000115786771113</c:v>
+                  <c:v>0.90129127420824506</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.29305531083713837</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>9.8708725791754978E-2</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>1.319933951198393E-2</c:v>
+                  <c:v>0.98680066048801607</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2291,7 +3042,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart16.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -3118,7 +3869,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'6'!$V$17</c:f>
+              <c:f>'6'!$W$17</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3195,7 +3946,7 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>'6'!$U$18:$U$26</c:f>
+              <c:f>'6'!$V$18:$V$26</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
@@ -3222,7 +3973,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'6'!$V$18:$V$26</c:f>
+              <c:f>'6'!$W$18:$W$26</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
@@ -3496,7 +4247,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'6'!$AC$16</c:f>
+              <c:f>'6'!$AD$16</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3529,7 +4280,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'6'!$AB$17:$AB$22</c:f>
+              <c:f>'6'!$AC$17:$AC$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -3556,7 +4307,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'6'!$AC$17:$AC$22</c:f>
+              <c:f>'6'!$AD$17:$AD$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -3787,6 +4538,373 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="8.5054680664916893E-3"/>
+                  <c:y val="-0.18292979002624671"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'6'!$P$2:$P$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>9149.2199999999993</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7836.22</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5594.22</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4518.92</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>390.63</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'6'!$S$2:$S$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.9996502494689522</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.94849121633689137</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.95669614187620411</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.88100273978849286</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.4819937756261423E-3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-8069-47EB-B168-7A375374D5FD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1063434607"/>
+        <c:axId val="1063433647"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1063434607"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1063433647"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1063433647"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1063434607"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
       <c:tx>
         <c:rich>
           <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
@@ -3939,13 +5057,13 @@
                   <c:v>90.038947747975925</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>63.56077105661538</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>11.239070366728425</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.85812064071644711</c:v>
+                  <c:v>1.2436811436632487</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4168,7 +5286,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -4325,20 +5443,20 @@
                   <c:v>78.290174217247227</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>55.267014596101255</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>9.7725350979665304</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.74614837402535861</c:v>
+                  <c:v>1.0813988373191517</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'5'!$T$9:$T$13</c:f>
+              <c:f>'5'!$U$9:$U$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
@@ -4554,7 +5672,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -4711,13 +5829,13 @@
                   <c:v>126.33578283455246</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>89.183625196083909</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>15.76980616307986</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.204049421088855</c:v>
+                  <c:v>1.7450385062368758</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4940,7 +6058,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -4954,6 +6072,44 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
+    <c:title>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.35469444444444442"/>
+          <c:y val="9.2592592592592587E-3"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
@@ -4963,6 +6119,17 @@
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'5'!$V$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>frac_discharge</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:noFill/>
@@ -5011,12 +6178,26 @@
             </c:spPr>
             <c:trendlineType val="linear"/>
             <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
             <c:dispEq val="1"/>
             <c:trendlineLbl>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="0.11042619592277809"/>
-                  <c:y val="-0.73588439441683817"/>
+                  <c:x val="-5.3275088186792184E-2"/>
+                  <c:y val="-9.7081875182268879E-2"/>
                 </c:manualLayout>
               </c:layout>
               <c:numFmt formatCode="General" sourceLinked="0"/>
@@ -5075,24 +6256,18 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'5'!$T$2:$T$6</c:f>
+              <c:f>'5'!$V$2:$V$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.81590896319190787</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.57597077830851362</c:v>
+                  <c:v>0.18409103680809216</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.10184546220848553</c:v>
+                  <c:v>0.89815453779151444</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>7.7760606912053946E-3</c:v>
+                  <c:v>0.98873009272267487</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5100,7 +6275,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-7C89-4549-93B2-4D45F33EDA72}"/>
+              <c16:uniqueId val="{00000000-C24D-4B59-A565-9C1F9EDF0141}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -5112,11 +6287,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="181741999"/>
-        <c:axId val="181742959"/>
+        <c:axId val="1063425967"/>
+        <c:axId val="1063426447"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="181741999"/>
+        <c:axId val="1063425967"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5173,12 +6348,12 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="181742959"/>
+        <c:crossAx val="1063426447"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="181742959"/>
+        <c:axId val="1063426447"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5235,390 +6410,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="181741999"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US"/>
-              <a:t>12/12/2025</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:noFill/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="1"/>
-            <c:dispEq val="1"/>
-            <c:trendlineLbl>
-              <c:numFmt formatCode="General" sourceLinked="0"/>
-              <c:spPr>
-                <a:noFill/>
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="65000"/>
-                          <a:lumOff val="35000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:latin typeface="+mn-lt"/>
-                      <a:ea typeface="+mn-ea"/>
-                      <a:cs typeface="+mn-cs"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
-                </a:p>
-              </c:txPr>
-            </c:trendlineLbl>
-          </c:trendline>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'9'!$M$9:$M$13</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>5.30642319963549</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>5.1472366477825098</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1.5550755002025809</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.52379027254782662</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>7.0041281406256914E-2</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'9'!$N$9:$N$13</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="1">
-                  <c:v>4.0599999999999996</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3.7</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>3.04</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>2.54</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-4FB9-4776-BEAA-B9FA9E002D5D}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="136937984"/>
-        <c:axId val="136938464"/>
-      </c:scatterChart>
-      <c:valAx>
-        <c:axId val="136937984"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="136938464"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:valAx>
-        <c:axId val="136938464"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="136937984"/>
+        <c:crossAx val="1063425967"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -5875,6 +6667,86 @@
 </file>
 
 <file path=xl/charts/colors14.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors15.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors16.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -9330,6 +10202,1038 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style15.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style16.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -13504,7 +15408,7 @@
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
+      <xdr:col>19</xdr:col>
       <xdr:colOff>600075</xdr:colOff>
       <xdr:row>34</xdr:row>
       <xdr:rowOff>142875</xdr:rowOff>
@@ -13534,13 +15438,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>19</xdr:col>
+      <xdr:col>20</xdr:col>
       <xdr:colOff>142875</xdr:colOff>
       <xdr:row>23</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>25</xdr:col>
+      <xdr:col>26</xdr:col>
       <xdr:colOff>209550</xdr:colOff>
       <xdr:row>34</xdr:row>
       <xdr:rowOff>57149</xdr:rowOff>
@@ -13570,13 +15474,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>25</xdr:col>
+      <xdr:col>26</xdr:col>
       <xdr:colOff>542925</xdr:colOff>
       <xdr:row>23</xdr:row>
       <xdr:rowOff>1587</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>30</xdr:col>
+      <xdr:col>31</xdr:col>
       <xdr:colOff>457200</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
@@ -13599,6 +15503,42 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>404812</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>160337</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>395287</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>49212</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Chart 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{280B94CF-93B2-D667-B042-AD6AFE370AC1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -13683,7 +15623,7 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>19</xdr:col>
+      <xdr:col>20</xdr:col>
       <xdr:colOff>593725</xdr:colOff>
       <xdr:row>11</xdr:row>
       <xdr:rowOff>82549</xdr:rowOff>
@@ -13719,23 +15659,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>132292</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>14816</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>478559</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>45317</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>338667</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>165099</xdr:rowOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>54264</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>121517</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Chart 2">
+        <xdr:cNvPr id="7" name="Chart 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D63E1CB9-21A7-2CD5-D045-4062029D3284}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A8460EEA-F143-2786-5B3B-81B72AAF9EE8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -13757,6 +15697,47 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>554037</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>173037</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>249237</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>61912</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D0E7CA7F-7AEB-2084-0048-9B37F271F6F9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -13802,7 +15783,7 @@
       <xdr:rowOff>19049</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
+      <xdr:col>20</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
       <xdr:row>23</xdr:row>
       <xdr:rowOff>47624</xdr:rowOff>
@@ -13832,13 +15813,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>19</xdr:col>
+      <xdr:col>20</xdr:col>
       <xdr:colOff>268287</xdr:colOff>
       <xdr:row>14</xdr:row>
       <xdr:rowOff>9524</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>23</xdr:col>
+      <xdr:col>24</xdr:col>
       <xdr:colOff>133350</xdr:colOff>
       <xdr:row>23</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
@@ -13904,16 +15885,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>542925</xdr:colOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>447675</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>1587</xdr:rowOff>
+      <xdr:rowOff>153987</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>30</xdr:col>
-      <xdr:colOff>238125</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>77787</xdr:rowOff>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>42862</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -13941,7 +15922,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -16302,7 +18283,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACBD19F5-47B4-4382-B740-81546DE76DA3}">
-  <dimension ref="A1:AC24"/>
+  <dimension ref="A1:AD24"/>
   <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="1" max="1" width="10.40625" bestFit="1" customWidth="1"/>
@@ -16312,9 +18293,10 @@
     <col min="15" max="15" width="10.7265625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="11.7265625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -16360,11 +18342,11 @@
       <c r="Q1" t="s">
         <v>6</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.75">
       <c r="A2" s="3">
         <v>45554</v>
       </c>
@@ -16414,11 +18396,15 @@
         <v>9204</v>
       </c>
       <c r="R2">
-        <f>Q2/$Q$7</f>
-        <v>3.4975053104776958E-4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.75">
+        <f>$Q$7-Q2</f>
+        <v>26306696</v>
+      </c>
+      <c r="S2">
+        <f>R2/$Q$7</f>
+        <v>0.9996502494689522</v>
+      </c>
+    </row>
+    <row r="3" spans="1:30" x14ac:dyDescent="0.75">
       <c r="A3" s="3">
         <v>45554</v>
       </c>
@@ -16468,11 +18454,15 @@
         <v>1355500</v>
       </c>
       <c r="R3">
-        <f t="shared" ref="R3:R7" si="0">Q3/$Q$7</f>
-        <v>5.1508783663108612E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.75">
+        <f t="shared" ref="R3:R6" si="0">$Q$7-Q3</f>
+        <v>24960400</v>
+      </c>
+      <c r="S3">
+        <f t="shared" ref="S3:S6" si="1">R3/$Q$7</f>
+        <v>0.94849121633689137</v>
+      </c>
+    </row>
+    <row r="4" spans="1:30" x14ac:dyDescent="0.75">
       <c r="A4" s="3">
         <v>45554</v>
       </c>
@@ -16520,10 +18510,14 @@
       </c>
       <c r="R4">
         <f t="shared" si="0"/>
-        <v>4.3303858123795877E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.75">
+        <v>25176320</v>
+      </c>
+      <c r="S4">
+        <f t="shared" si="1"/>
+        <v>0.95669614187620411</v>
+      </c>
+    </row>
+    <row r="5" spans="1:30" x14ac:dyDescent="0.75">
       <c r="A5" s="1">
         <v>45638</v>
       </c>
@@ -16574,10 +18568,14 @@
       </c>
       <c r="R5">
         <f t="shared" si="0"/>
-        <v>0.11899726021150711</v>
-      </c>
-    </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.75">
+        <v>23184380</v>
+      </c>
+      <c r="S5">
+        <f t="shared" si="1"/>
+        <v>0.88100273978849286</v>
+      </c>
+    </row>
+    <row r="6" spans="1:30" x14ac:dyDescent="0.75">
       <c r="A6" s="1">
         <v>45638</v>
       </c>
@@ -16628,10 +18626,14 @@
       </c>
       <c r="R6">
         <f t="shared" si="0"/>
-        <v>0.99851800622437381</v>
-      </c>
-    </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.75">
+        <v>39000</v>
+      </c>
+      <c r="S6">
+        <f t="shared" si="1"/>
+        <v>1.4819937756261423E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:30" x14ac:dyDescent="0.75">
       <c r="A7" s="1">
         <v>45638</v>
       </c>
@@ -16680,12 +18682,8 @@
       <c r="Q7">
         <v>26315900</v>
       </c>
-      <c r="R7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.75">
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.75">
       <c r="A8" s="3">
         <v>45708</v>
       </c>
@@ -16711,7 +18709,7 @@
         <v>71.468085561174107</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.75">
       <c r="A9" s="3">
         <v>45708</v>
       </c>
@@ -16756,7 +18754,7 @@
       </c>
       <c r="P9" s="2"/>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.75">
       <c r="A10" s="3">
         <v>45708</v>
       </c>
@@ -16807,7 +18805,7 @@
         <v>2.9536471148044623E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.75">
       <c r="A11" s="1">
         <v>45727</v>
       </c>
@@ -16839,23 +18837,23 @@
         <v>5.1508783663108612E-2</v>
       </c>
       <c r="L11">
-        <f t="shared" ref="L11:L14" si="1">K11*$L$15</f>
+        <f t="shared" ref="L11:L14" si="2">K11*$L$15</f>
         <v>17.867953999719802</v>
       </c>
       <c r="M11">
-        <f t="shared" ref="M11:M14" si="2">K11*$M$15</f>
+        <f t="shared" ref="M11:M14" si="3">K11*$M$15</f>
         <v>0.28484444209033927</v>
       </c>
       <c r="N11">
-        <f t="shared" ref="N11:N14" si="3">$K11*$N$15</f>
+        <f t="shared" ref="N11:N14" si="4">$K11*$N$15</f>
         <v>3.6812341579870531</v>
       </c>
       <c r="O11">
-        <f t="shared" ref="O11:O14" si="4">$K11*$O$15</f>
+        <f t="shared" ref="O11:O14" si="5">$K11*$O$15</f>
         <v>4.3499224946951855</v>
       </c>
     </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.75">
       <c r="A12" s="1">
         <v>45727</v>
       </c>
@@ -16887,23 +18885,23 @@
         <v>4.3303858123795877E-2</v>
       </c>
       <c r="L12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>15.021735904832674</v>
       </c>
       <c r="M12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.23947106552365088</v>
       </c>
       <c r="N12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3.0948438375203882</v>
       </c>
       <c r="O12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3.6570156226519654</v>
       </c>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.75">
       <c r="A13" s="5">
         <v>45554</v>
       </c>
@@ -16938,23 +18936,23 @@
         <v>0.11899726021150711</v>
       </c>
       <c r="L13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>41.279126011953196</v>
       </c>
       <c r="M13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.65805685525248192</v>
       </c>
       <c r="N13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>8.5045063743412896</v>
       </c>
       <c r="O13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>10.049331826328194</v>
       </c>
     </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:30" x14ac:dyDescent="0.75">
       <c r="A14" s="5">
         <v>45554</v>
       </c>
@@ -16989,23 +18987,23 @@
         <v>0.99851800622437381</v>
       </c>
       <c r="L14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>346.37730760253578</v>
       </c>
       <c r="M14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.5218214093424089</v>
       </c>
       <c r="N14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>71.36217030321653</v>
       </c>
       <c r="O14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>84.324956400483899</v>
       </c>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.75">
       <c r="A15" s="5">
         <v>45554</v>
       </c>
@@ -17048,7 +19046,7 @@
         <v>84.450110939246798</v>
       </c>
     </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.75">
       <c r="A16" s="2">
         <v>45638</v>
       </c>
@@ -17073,14 +19071,14 @@
       <c r="H16">
         <v>5.5300168599079003</v>
       </c>
-      <c r="AB16" s="2" t="s">
+      <c r="AC16" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="AC16" s="6" t="s">
+      <c r="AD16" s="6" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:29" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:30" x14ac:dyDescent="0.75">
       <c r="A17" s="2">
         <v>45638</v>
       </c>
@@ -17117,21 +19115,22 @@
       <c r="Q17" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="U17" s="2" t="s">
+      <c r="R17" s="6"/>
+      <c r="V17" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="V17" s="6" t="s">
+      <c r="W17" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="AB17">
-        <f t="shared" ref="AB17:AB22" si="5">$K10*$O$15</f>
+      <c r="AC17">
+        <f t="shared" ref="AC17:AC22" si="6">$K10*$O$15</f>
         <v>2.9536471148044623E-2</v>
       </c>
-      <c r="AC17">
+      <c r="AD17">
         <v>2.7</v>
       </c>
     </row>
-    <row r="18" spans="1:29" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:30" x14ac:dyDescent="0.75">
       <c r="A18" s="2">
         <v>45638</v>
       </c>
@@ -17157,29 +19156,29 @@
         <v>11</v>
       </c>
       <c r="L18">
-        <f t="shared" ref="L18:L23" si="6">$K10*$L$15</f>
+        <f t="shared" ref="L18:L23" si="7">$K10*$L$15</f>
         <v>0.12132545083985322</v>
       </c>
       <c r="P18">
-        <f t="shared" ref="P18:P23" si="7">$K10*$M$15</f>
+        <f t="shared" ref="P18:P23" si="8">$K10*$M$15</f>
         <v>1.9341263334559074E-3</v>
       </c>
-      <c r="U18">
-        <f t="shared" ref="U18:U23" si="8">$K10*$N$15</f>
+      <c r="V18">
+        <f t="shared" ref="V18:V23" si="9">$K10*$N$15</f>
         <v>2.4996000877988075E-2</v>
       </c>
-      <c r="V18">
+      <c r="W18">
         <v>2.77</v>
       </c>
-      <c r="AB18">
-        <f t="shared" si="5"/>
+      <c r="AC18">
+        <f t="shared" si="6"/>
         <v>4.3499224946951855</v>
       </c>
-      <c r="AC18">
+      <c r="AD18">
         <v>1.89</v>
       </c>
     </row>
-    <row r="19" spans="1:29" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:30" x14ac:dyDescent="0.75">
       <c r="A19" s="5">
         <v>45708</v>
       </c>
@@ -17211,32 +19210,32 @@
         <v>10</v>
       </c>
       <c r="L19">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>17.867953999719802</v>
       </c>
       <c r="M19">
         <v>0.56000000000000005</v>
       </c>
       <c r="P19">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.28484444209033927</v>
       </c>
       <c r="Q19">
         <v>1.1200000000000001</v>
       </c>
-      <c r="U19">
-        <f t="shared" si="8"/>
+      <c r="V19">
+        <f t="shared" si="9"/>
         <v>3.6812341579870531</v>
       </c>
-      <c r="V19">
+      <c r="W19">
         <v>1.62</v>
       </c>
-      <c r="AB19">
-        <f t="shared" si="5"/>
+      <c r="AC19">
+        <f t="shared" si="6"/>
         <v>3.6570156226519654</v>
       </c>
     </row>
-    <row r="20" spans="1:29" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:30" x14ac:dyDescent="0.75">
       <c r="A20" s="5">
         <v>45708</v>
       </c>
@@ -17268,35 +19267,35 @@
         <v>9</v>
       </c>
       <c r="L20">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>15.021735904832674</v>
       </c>
       <c r="M20">
         <v>1.22</v>
       </c>
       <c r="P20">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.23947106552365088</v>
       </c>
       <c r="Q20">
         <v>1.7</v>
       </c>
-      <c r="U20">
-        <f t="shared" si="8"/>
+      <c r="V20">
+        <f t="shared" si="9"/>
         <v>3.0948438375203882</v>
       </c>
-      <c r="V20">
+      <c r="W20">
         <v>4.72</v>
       </c>
-      <c r="AB20">
-        <f t="shared" si="5"/>
+      <c r="AC20">
+        <f t="shared" si="6"/>
         <v>10.049331826328194</v>
       </c>
-      <c r="AC20">
+      <c r="AD20">
         <v>4.2699999999999996</v>
       </c>
     </row>
-    <row r="21" spans="1:29" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:30" x14ac:dyDescent="0.75">
       <c r="A21" s="5">
         <v>45708</v>
       </c>
@@ -17324,32 +19323,32 @@
         <v>11</v>
       </c>
       <c r="L21">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>41.279126011953196</v>
       </c>
       <c r="M21">
         <v>1.29</v>
       </c>
       <c r="P21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.65805685525248192</v>
       </c>
-      <c r="U21">
-        <f t="shared" si="8"/>
+      <c r="V21">
+        <f t="shared" si="9"/>
         <v>8.5045063743412896</v>
       </c>
-      <c r="V21">
+      <c r="W21">
         <v>4.04</v>
       </c>
-      <c r="AB21">
-        <f t="shared" si="5"/>
+      <c r="AC21">
+        <f t="shared" si="6"/>
         <v>84.324956400483899</v>
       </c>
-      <c r="AC21">
+      <c r="AD21">
         <v>3.81</v>
       </c>
     </row>
-    <row r="22" spans="1:29" x14ac:dyDescent="0.75">
+    <row r="22" spans="1:30" x14ac:dyDescent="0.75">
       <c r="A22" s="2">
         <v>45727</v>
       </c>
@@ -17381,35 +19380,35 @@
         <v>10</v>
       </c>
       <c r="L22">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>346.37730760253578</v>
       </c>
       <c r="M22">
         <v>2.06</v>
       </c>
       <c r="P22">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>5.5218214093424089</v>
       </c>
       <c r="Q22">
         <v>4.3099999999999996</v>
       </c>
-      <c r="U22">
-        <f t="shared" si="8"/>
+      <c r="V22">
+        <f t="shared" si="9"/>
         <v>71.36217030321653</v>
       </c>
-      <c r="V22">
+      <c r="W22">
         <v>4.12</v>
       </c>
-      <c r="AB22">
-        <f t="shared" si="5"/>
+      <c r="AC22">
+        <f t="shared" si="6"/>
         <v>84.450110939246798</v>
       </c>
-      <c r="AC22">
+      <c r="AD22">
         <v>2.62</v>
       </c>
     </row>
-    <row r="23" spans="1:29" x14ac:dyDescent="0.75">
+    <row r="23" spans="1:30" x14ac:dyDescent="0.75">
       <c r="A23" s="2">
         <v>45727</v>
       </c>
@@ -17441,28 +19440,28 @@
         <v>8</v>
       </c>
       <c r="L23">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>346.89139849592499</v>
       </c>
       <c r="M23">
         <v>2.2999999999999998</v>
       </c>
       <c r="P23">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>5.5300168599079003</v>
       </c>
       <c r="Q23">
         <v>3.72</v>
       </c>
-      <c r="U23">
-        <f t="shared" si="8"/>
+      <c r="V23">
+        <f t="shared" si="9"/>
         <v>71.468085561174107</v>
       </c>
-      <c r="V23">
+      <c r="W23">
         <v>4.0599999999999996</v>
       </c>
     </row>
-    <row r="24" spans="1:29" x14ac:dyDescent="0.75">
+    <row r="24" spans="1:30" x14ac:dyDescent="0.75">
       <c r="A24" s="2">
         <v>45727</v>
       </c>
@@ -17500,6 +19499,8 @@
     <col min="16" max="16" width="13" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="10.7265625" customWidth="1"/>
     <col min="19" max="19" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.86328125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="38.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.75">
@@ -17546,7 +19547,13 @@
         <v>6</v>
       </c>
       <c r="T1" t="s">
+        <v>68</v>
+      </c>
+      <c r="U1" t="s">
         <v>31</v>
+      </c>
+      <c r="V1" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.75">
@@ -17590,13 +19597,9 @@
       <c r="S2">
         <v>17795000</v>
       </c>
-      <c r="T2">
-        <f t="shared" ref="T2:T5" si="0">S2/$S$2</f>
+      <c r="U2">
+        <f t="shared" ref="U2:U5" si="0">S2/$S$2</f>
         <v>1</v>
-      </c>
-      <c r="U2">
-        <f>S2/1000</f>
-        <v>17795</v>
       </c>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.75">
@@ -17647,12 +19650,16 @@
         <v>14519100</v>
       </c>
       <c r="T3">
+        <f>$S$2-S3</f>
+        <v>3275900</v>
+      </c>
+      <c r="U3">
         <f t="shared" si="0"/>
         <v>0.81590896319190787</v>
       </c>
-      <c r="U3">
-        <f t="shared" ref="U3:U6" si="1">S3/1000</f>
-        <v>14519.1</v>
+      <c r="V3">
+        <f>T3/$S$2</f>
+        <v>0.18409103680809216</v>
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.75">
@@ -17702,16 +19709,13 @@
       <c r="R4">
         <v>2467.91</v>
       </c>
-      <c r="S4">
-        <v>10249400</v>
-      </c>
       <c r="T4">
+        <f t="shared" ref="T4:T5" si="1">$S$2-S4</f>
+        <v>17795000</v>
+      </c>
+      <c r="U4">
         <f t="shared" si="0"/>
-        <v>0.57597077830851362</v>
-      </c>
-      <c r="U4">
-        <f t="shared" si="1"/>
-        <v>10249.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.75">
@@ -17765,12 +19769,16 @@
         <v>1812340</v>
       </c>
       <c r="T5">
+        <f t="shared" si="1"/>
+        <v>15982660</v>
+      </c>
+      <c r="U5">
         <f t="shared" si="0"/>
         <v>0.10184546220848553</v>
       </c>
-      <c r="U5">
-        <f t="shared" si="1"/>
-        <v>1812.34</v>
+      <c r="V5">
+        <f t="shared" ref="V5" si="2">T5/$S$2</f>
+        <v>0.89815453779151444</v>
       </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.75">
@@ -17821,15 +19829,19 @@
         <v>6130.37</v>
       </c>
       <c r="S6">
-        <v>138375</v>
+        <v>200548</v>
       </c>
       <c r="T6">
+        <f>$S$2-S6</f>
+        <v>17594452</v>
+      </c>
+      <c r="U6">
         <f>S6/$S$2</f>
-        <v>7.7760606912053946E-3</v>
-      </c>
-      <c r="U6">
-        <f t="shared" si="1"/>
-        <v>138.375</v>
+        <v>1.1269907277325091E-2</v>
+      </c>
+      <c r="V6">
+        <f>T6/$S$2</f>
+        <v>0.98873009272267487</v>
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.75">
@@ -17899,7 +19911,7 @@
       <c r="S8" t="s">
         <v>21</v>
       </c>
-      <c r="T8" s="6" t="s">
+      <c r="U8" s="6" t="s">
         <v>24</v>
       </c>
       <c r="W8" t="s">
@@ -17941,25 +19953,25 @@
         <v>15</v>
       </c>
       <c r="L9" s="7">
-        <f>$T2*$H$2</f>
+        <f>$U2*$H$2</f>
         <v>110.354159360789</v>
       </c>
       <c r="M9" s="7">
         <v>5.1100000000000003</v>
       </c>
       <c r="O9">
-        <f>$T2*$H$11</f>
+        <f>$U2*$H$11</f>
         <v>163.31096051543099</v>
       </c>
       <c r="S9">
-        <f>$T2*$H$6</f>
+        <f>$U2*$H$6</f>
         <v>95.954546094173494</v>
       </c>
-      <c r="T9">
+      <c r="U9">
         <v>7</v>
       </c>
       <c r="W9">
-        <f>$T2*$H$14</f>
+        <f>$U2*$H$14</f>
         <v>154.84053801825601</v>
       </c>
       <c r="X9">
@@ -17998,25 +20010,25 @@
         <v>9</v>
       </c>
       <c r="L10" s="7">
-        <f>$T3*$H$2</f>
+        <f>$U3*$H$2</f>
         <v>90.038947747975925</v>
       </c>
       <c r="M10" s="7">
         <v>4.01</v>
       </c>
       <c r="O10">
-        <f t="shared" ref="O10:O13" si="2">$T3*$H$11</f>
+        <f>$U3*$H$11</f>
         <v>133.24687647201989</v>
       </c>
       <c r="S10">
-        <f t="shared" ref="S10:S13" si="3">$T3*$H$6</f>
+        <f>$U3*$H$6</f>
         <v>78.290174217247227</v>
       </c>
-      <c r="T10">
+      <c r="U10">
         <v>6.1</v>
       </c>
       <c r="W10">
-        <f t="shared" ref="W10:W13" si="4">$T3*$H$14</f>
+        <f>$U3*$H$14</f>
         <v>126.33578283455246</v>
       </c>
       <c r="X10">
@@ -18055,29 +20067,29 @@
         <v>8</v>
       </c>
       <c r="L11" s="7">
-        <f>$T4*$H$2</f>
-        <v>63.56077105661538</v>
+        <f>$U4*$H$2</f>
+        <v>0</v>
       </c>
       <c r="M11" s="7">
         <v>2.68</v>
       </c>
       <c r="O11">
-        <f t="shared" si="2"/>
-        <v>94.062341034383721</v>
+        <f>$U4*$H$11</f>
+        <v>0</v>
       </c>
       <c r="P11">
         <v>6.12</v>
       </c>
       <c r="S11">
-        <f t="shared" si="3"/>
-        <v>55.267014596101255</v>
-      </c>
-      <c r="T11">
+        <f>$U4*$H$6</f>
+        <v>0</v>
+      </c>
+      <c r="U11">
         <v>6.04</v>
       </c>
       <c r="W11">
-        <f t="shared" si="4"/>
-        <v>89.183625196083909</v>
+        <f>$U4*$H$14</f>
+        <v>0</v>
       </c>
       <c r="X11">
         <v>4.41</v>
@@ -18115,28 +20127,28 @@
         <v>10</v>
       </c>
       <c r="L12" s="7">
-        <f>$T5*$H$2</f>
+        <f>$U5*$H$2</f>
         <v>11.239070366728425</v>
       </c>
       <c r="M12" s="7">
         <v>0.67</v>
       </c>
       <c r="O12">
-        <f t="shared" si="2"/>
+        <f>$U5*$H$11</f>
         <v>16.632480257405799</v>
       </c>
       <c r="P12">
         <v>3.19</v>
       </c>
       <c r="S12">
-        <f t="shared" si="3"/>
+        <f>$U5*$H$6</f>
         <v>9.7725350979665304</v>
       </c>
-      <c r="T12">
+      <c r="U12">
         <v>3.68</v>
       </c>
       <c r="W12">
-        <f t="shared" si="4"/>
+        <f>$U5*$H$14</f>
         <v>15.76980616307986</v>
       </c>
       <c r="X12">
@@ -18175,29 +20187,29 @@
         <v>11</v>
       </c>
       <c r="L13" s="7">
-        <f>$T6*$H$2</f>
-        <v>0.85812064071644711</v>
+        <f>$U6*$H$2</f>
+        <v>1.2436811436632487</v>
       </c>
       <c r="M13" s="7">
         <v>0.6</v>
       </c>
       <c r="O13">
-        <f t="shared" si="2"/>
-        <v>1.2699159405070393</v>
+        <f>$U6*$H$11</f>
+        <v>1.8404993823798064</v>
       </c>
       <c r="P13">
         <v>3.96</v>
       </c>
       <c r="S13">
-        <f t="shared" si="3"/>
-        <v>0.74614837402535861</v>
-      </c>
-      <c r="T13">
+        <f>$U6*$H$6</f>
+        <v>1.0813988373191517</v>
+      </c>
+      <c r="U13">
         <v>5.8</v>
       </c>
       <c r="W13">
-        <f t="shared" si="4"/>
-        <v>1.204049421088855</v>
+        <f>$U6*$H$14</f>
+        <v>1.7450385062368758</v>
       </c>
       <c r="X13">
         <v>1.52</v>
@@ -18322,822 +20334,99 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0CB5E58-BD10-4113-A538-64E594317AC5}">
-  <dimension ref="A1:T19"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87F33DFE-17D7-41AE-9077-36D7A41FD6EB}">
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="10.26953125" bestFit="1" customWidth="1"/>
-    <col min="12" max="15" width="10.26953125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.26953125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.6796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.58984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.6796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A2">
+        <v>17795000</v>
+      </c>
+      <c r="B2">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="L1" s="1">
-        <v>45727</v>
-      </c>
-      <c r="M1" s="1">
-        <v>45708</v>
-      </c>
-      <c r="N1" s="1">
-        <v>45638</v>
-      </c>
-      <c r="O1" s="1">
-        <v>45554</v>
-      </c>
-      <c r="P1" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>5</v>
-      </c>
-      <c r="R1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.75">
-      <c r="A2" s="1">
-        <v>45554</v>
-      </c>
-      <c r="B2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2">
-        <v>1.2</v>
-      </c>
-      <c r="E2">
-        <v>3.57</v>
-      </c>
-      <c r="F2">
-        <v>904.88</v>
-      </c>
-      <c r="G2">
-        <v>19268200</v>
-      </c>
-      <c r="H2">
-        <v>100.03049449091</v>
-      </c>
-      <c r="J2" t="s">
-        <v>16</v>
-      </c>
-      <c r="K2" t="s">
-        <v>15</v>
-      </c>
-      <c r="L2">
-        <v>6.37</v>
-      </c>
-      <c r="M2">
-        <v>7.22</v>
-      </c>
-      <c r="P2">
-        <v>19864100</v>
-      </c>
-      <c r="Q2">
-        <v>0</v>
-      </c>
-      <c r="R2">
-        <f>P2/$P$2</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.75">
-      <c r="A3" s="1">
-        <v>45554</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" t="s">
-        <v>8</v>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A3">
+        <v>14519100</v>
+      </c>
+      <c r="B3">
+        <v>1267.3699999999999</v>
+      </c>
+      <c r="C3">
+        <f>$A$2-A3</f>
+        <v>3275900</v>
       </c>
       <c r="D3">
-        <v>0.38</v>
-      </c>
-      <c r="E3">
-        <v>3.76</v>
-      </c>
-      <c r="F3">
-        <v>2002.8</v>
-      </c>
-      <c r="G3">
-        <v>5821280</v>
-      </c>
-      <c r="H3">
-        <v>100.03049449091</v>
-      </c>
-      <c r="J3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K3" t="s">
-        <v>9</v>
-      </c>
-      <c r="L3">
-        <v>3.77</v>
-      </c>
-      <c r="M3">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="N3">
-        <v>4.0599999999999996</v>
-      </c>
-      <c r="O3">
-        <v>1.2</v>
-      </c>
-      <c r="P3">
-        <v>19268200</v>
-      </c>
-      <c r="Q3">
-        <v>904.88</v>
-      </c>
-      <c r="R3">
-        <f t="shared" ref="R3:R6" si="0">P3/$P$2</f>
-        <v>0.97000115786771113</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.75">
-      <c r="A4" s="1">
-        <v>45554</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" t="s">
-        <v>10</v>
+        <f>C3/$A$2</f>
+        <v>0.18409103680809216</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A4">
+        <v>10249400</v>
+      </c>
+      <c r="B4">
+        <v>2467.91</v>
+      </c>
+      <c r="C4">
+        <f t="shared" ref="C4:C6" si="0">$A$2-A4</f>
+        <v>7545600</v>
       </c>
       <c r="D4">
-        <v>0.36</v>
-      </c>
-      <c r="E4">
-        <v>3.81</v>
-      </c>
-      <c r="F4">
-        <v>3140.96</v>
-      </c>
-      <c r="G4">
-        <v>1960760</v>
-      </c>
-      <c r="H4">
-        <v>100.03049449091</v>
-      </c>
-      <c r="J4" t="s">
-        <v>16</v>
-      </c>
-      <c r="K4" t="s">
-        <v>8</v>
-      </c>
-      <c r="L4">
-        <v>3.04</v>
-      </c>
-      <c r="M4">
-        <v>3.16</v>
-      </c>
-      <c r="N4">
-        <v>3.7</v>
-      </c>
-      <c r="O4">
-        <v>0.38</v>
-      </c>
-      <c r="P4">
-        <v>5821280</v>
-      </c>
-      <c r="Q4">
-        <v>2002.8</v>
-      </c>
-      <c r="R4">
+        <f t="shared" ref="D4:D6" si="1">C4/$A$2</f>
+        <v>0.42402922169148638</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A5">
+        <v>1812340</v>
+      </c>
+      <c r="B5">
+        <v>4497.8599999999997</v>
+      </c>
+      <c r="C5">
         <f t="shared" si="0"/>
-        <v>0.29305531083713837</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.75">
-      <c r="A5" s="1">
-        <v>45554</v>
-      </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5">
-        <v>8475.9599999999991</v>
-      </c>
-      <c r="G5">
-        <v>262193</v>
-      </c>
-      <c r="H5">
-        <v>100.03049449091</v>
-      </c>
-      <c r="J5" t="s">
-        <v>16</v>
-      </c>
-      <c r="K5" t="s">
-        <v>10</v>
-      </c>
-      <c r="L5">
-        <v>1.99</v>
-      </c>
-      <c r="M5">
-        <v>1.52</v>
-      </c>
-      <c r="N5">
-        <v>3.04</v>
-      </c>
-      <c r="O5">
-        <v>0.36</v>
-      </c>
-      <c r="P5">
-        <v>1960760</v>
-      </c>
-      <c r="Q5">
-        <v>3140.96</v>
-      </c>
-      <c r="R5">
+        <v>15982660</v>
+      </c>
+      <c r="D5">
+        <f t="shared" si="1"/>
+        <v>0.89815453779151444</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A6">
+        <v>138375</v>
+      </c>
+      <c r="B6">
+        <v>6130.37</v>
+      </c>
+      <c r="C6">
         <f t="shared" si="0"/>
-        <v>9.8708725791754978E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.75">
-      <c r="A6" s="3">
-        <v>45638</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="4">
-        <v>4.0599999999999996</v>
-      </c>
-      <c r="E6" s="4">
-        <v>3.6</v>
-      </c>
-      <c r="F6" s="4">
-        <v>904.88</v>
-      </c>
-      <c r="G6" s="4">
-        <v>19268200</v>
-      </c>
-      <c r="H6" s="4">
-        <v>5.30642319963549</v>
-      </c>
-      <c r="J6" t="s">
-        <v>16</v>
-      </c>
-      <c r="K6" t="s">
-        <v>11</v>
-      </c>
-      <c r="L6">
-        <v>8.9</v>
-      </c>
-      <c r="M6">
-        <v>1.1100000000000001</v>
-      </c>
-      <c r="N6">
-        <v>2.54</v>
-      </c>
-      <c r="P6">
-        <v>262193</v>
-      </c>
-      <c r="Q6">
-        <v>8475.9599999999991</v>
-      </c>
-      <c r="R6">
-        <f t="shared" si="0"/>
-        <v>1.319933951198393E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.75">
-      <c r="A7" s="3">
-        <v>45638</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="4">
-        <v>3.7</v>
-      </c>
-      <c r="E7" s="4">
-        <v>4.0199999999999996</v>
-      </c>
-      <c r="F7" s="4">
-        <v>2002.8</v>
-      </c>
-      <c r="G7" s="4">
-        <v>5821280</v>
-      </c>
-      <c r="H7" s="4">
-        <v>5.30642319963549</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.75">
-      <c r="A8" s="3">
-        <v>45638</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" s="4">
-        <v>3.04</v>
-      </c>
-      <c r="E8" s="4">
-        <v>4.5199999999999996</v>
-      </c>
-      <c r="F8" s="4">
-        <v>3140.96</v>
-      </c>
-      <c r="G8" s="4">
-        <v>1960760</v>
-      </c>
-      <c r="H8" s="4">
-        <v>5.30642319963549</v>
-      </c>
-      <c r="J8" t="s">
-        <v>21</v>
-      </c>
-      <c r="K8" t="s">
-        <v>26</v>
-      </c>
-      <c r="M8" t="s">
-        <v>21</v>
-      </c>
-      <c r="N8" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="P8" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="S8" t="s">
-        <v>21</v>
-      </c>
-      <c r="T8" s="6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.75">
-      <c r="A9" s="3">
-        <v>45638</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D9" s="4">
-        <v>2.54</v>
-      </c>
-      <c r="E9" s="4">
-        <v>4.5599999999999996</v>
-      </c>
-      <c r="F9" s="4">
-        <v>8475.9599999999991</v>
-      </c>
-      <c r="G9" s="4">
-        <v>262193</v>
-      </c>
-      <c r="H9" s="4">
-        <v>5.30642319963549</v>
-      </c>
-      <c r="I9" t="s">
-        <v>15</v>
-      </c>
-      <c r="J9">
-        <f>$R2*$H$2</f>
-        <v>100.03049449091</v>
-      </c>
-      <c r="M9">
-        <f>$R2*$H$6</f>
-        <v>5.30642319963549</v>
-      </c>
-      <c r="P9">
-        <f>$R2*$H$10</f>
-        <v>37.743591811441398</v>
-      </c>
-      <c r="Q9">
-        <v>7.22</v>
-      </c>
-      <c r="S9">
-        <f>$R2*$H$15</f>
-        <v>68.679981822201199</v>
-      </c>
-      <c r="T9">
-        <v>6.37</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.75">
-      <c r="A10" s="1">
-        <v>45708</v>
-      </c>
-      <c r="B10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10">
-        <v>7.22</v>
-      </c>
-      <c r="E10">
-        <v>3.71</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>19864100</v>
-      </c>
-      <c r="H10">
-        <v>37.743591811441398</v>
-      </c>
-      <c r="I10" t="s">
-        <v>9</v>
-      </c>
-      <c r="J10">
-        <f t="shared" ref="J10:J13" si="1">$R3*$H$2</f>
-        <v>97.029695478262397</v>
-      </c>
-      <c r="K10">
-        <v>1.2</v>
-      </c>
-      <c r="M10">
-        <f t="shared" ref="M10:M13" si="2">$R3*$H$6</f>
-        <v>5.1472366477825098</v>
-      </c>
-      <c r="N10">
-        <v>4.0599999999999996</v>
-      </c>
-      <c r="P10">
-        <f t="shared" ref="P10:P12" si="3">$R3*$H$10</f>
-        <v>36.61132775918442</v>
-      </c>
-      <c r="Q10">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="S10">
-        <f t="shared" ref="S10:S13" si="4">$R3*$H$15</f>
-        <v>66.61966188986851</v>
-      </c>
-      <c r="T10">
-        <v>3.77</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.75">
-      <c r="A11" s="1">
-        <v>45708</v>
-      </c>
-      <c r="B11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="E11">
-        <v>3.73</v>
-      </c>
-      <c r="F11">
-        <v>904.88</v>
-      </c>
-      <c r="G11">
-        <v>19268200</v>
-      </c>
-      <c r="H11">
-        <v>37.743591811441398</v>
-      </c>
-      <c r="I11" t="s">
-        <v>8</v>
-      </c>
-      <c r="J11">
+        <v>17656625</v>
+      </c>
+      <c r="D6">
         <f t="shared" si="1"/>
-        <v>29.314467656226288</v>
-      </c>
-      <c r="K11">
-        <v>0.38</v>
-      </c>
-      <c r="M11">
-        <f t="shared" si="2"/>
-        <v>1.5550755002025809</v>
-      </c>
-      <c r="N11">
-        <v>3.7</v>
-      </c>
-      <c r="P11">
-        <f t="shared" si="3"/>
-        <v>11.06096003041203</v>
-      </c>
-      <c r="Q11">
-        <v>3.16</v>
-      </c>
-      <c r="S11">
-        <f t="shared" si="4"/>
-        <v>20.127033421194184</v>
-      </c>
-      <c r="T11">
-        <v>3.04</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.75">
-      <c r="A12" s="1">
-        <v>45708</v>
-      </c>
-      <c r="B12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12">
-        <v>3.16</v>
-      </c>
-      <c r="E12">
-        <v>3.86</v>
-      </c>
-      <c r="F12">
-        <v>2002.8</v>
-      </c>
-      <c r="G12">
-        <v>5821280</v>
-      </c>
-      <c r="H12">
-        <v>37.743591811441398</v>
-      </c>
-      <c r="I12" t="s">
-        <v>10</v>
-      </c>
-      <c r="J12">
-        <f t="shared" si="1"/>
-        <v>9.873882651516892</v>
-      </c>
-      <c r="K12">
-        <v>0.36</v>
-      </c>
-      <c r="M12">
-        <f t="shared" si="2"/>
-        <v>0.52379027254782662</v>
-      </c>
-      <c r="N12">
-        <v>3.04</v>
-      </c>
-      <c r="P12">
-        <f t="shared" si="3"/>
-        <v>3.7256218545114974</v>
-      </c>
-      <c r="Q12">
-        <v>1.52</v>
-      </c>
-      <c r="S12">
-        <f t="shared" si="4"/>
-        <v>6.7793134930703749</v>
-      </c>
-      <c r="T12">
-        <v>1.99</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.75">
-      <c r="A13" s="1">
-        <v>45708</v>
-      </c>
-      <c r="B13" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" t="s">
-        <v>10</v>
-      </c>
-      <c r="D13">
-        <v>1.52</v>
-      </c>
-      <c r="E13">
-        <v>3.97</v>
-      </c>
-      <c r="F13">
-        <v>3140.96</v>
-      </c>
-      <c r="G13">
-        <v>1960760</v>
-      </c>
-      <c r="H13">
-        <v>37.743591811441398</v>
-      </c>
-      <c r="I13" t="s">
-        <v>11</v>
-      </c>
-      <c r="J13">
-        <f t="shared" si="1"/>
-        <v>1.3203364583371593</v>
-      </c>
-      <c r="M13">
-        <f t="shared" si="2"/>
-        <v>7.0041281406256914E-2</v>
-      </c>
-      <c r="N13">
-        <v>2.54</v>
-      </c>
-      <c r="P13">
-        <f>$R6*$H$10</f>
-        <v>0.49819048272095157</v>
-      </c>
-      <c r="Q13">
-        <v>1.1100000000000001</v>
-      </c>
-      <c r="S13">
-        <f t="shared" si="4"/>
-        <v>0.90653039774811839</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.75">
-      <c r="A14" s="1">
-        <v>45708</v>
-      </c>
-      <c r="B14" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" t="s">
-        <v>11</v>
-      </c>
-      <c r="D14">
-        <v>1.1100000000000001</v>
-      </c>
-      <c r="E14">
-        <v>5.44</v>
-      </c>
-      <c r="F14">
-        <v>8475.9599999999991</v>
-      </c>
-      <c r="G14">
-        <v>262193</v>
-      </c>
-      <c r="H14">
-        <v>37.743591811441398</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.75">
-      <c r="A15" s="3">
-        <v>45727</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D15" s="4">
-        <v>6.37</v>
-      </c>
-      <c r="E15" s="4">
-        <v>3.53</v>
-      </c>
-      <c r="F15" s="4">
-        <v>0</v>
-      </c>
-      <c r="G15" s="4">
-        <v>19864100</v>
-      </c>
-      <c r="H15" s="4">
-        <v>68.679981822201199</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.75">
-      <c r="A16" s="3">
-        <v>45727</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D16" s="4">
-        <v>3.77</v>
-      </c>
-      <c r="E16" s="4">
-        <v>3.54</v>
-      </c>
-      <c r="F16" s="4">
-        <v>904.88</v>
-      </c>
-      <c r="G16" s="4">
-        <v>19268200</v>
-      </c>
-      <c r="H16" s="4">
-        <v>68.679981822201199</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.75">
-      <c r="A17" s="3">
-        <v>45727</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D17" s="4">
-        <v>3.04</v>
-      </c>
-      <c r="E17" s="4">
-        <v>3.72</v>
-      </c>
-      <c r="F17" s="4">
-        <v>2002.8</v>
-      </c>
-      <c r="G17" s="4">
-        <v>5821280</v>
-      </c>
-      <c r="H17" s="4">
-        <v>68.679981822201199</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.75">
-      <c r="A18" s="3">
-        <v>45727</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D18" s="4">
-        <v>1.99</v>
-      </c>
-      <c r="E18" s="4">
-        <v>3.61</v>
-      </c>
-      <c r="F18" s="4">
-        <v>3140.96</v>
-      </c>
-      <c r="G18" s="4">
-        <v>1960760</v>
-      </c>
-      <c r="H18" s="4">
-        <v>68.679981822201199</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.75">
-      <c r="A19" s="3">
-        <v>45727</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D19" s="4">
-        <v>8.9</v>
-      </c>
-      <c r="E19" s="4">
-        <v>5.89</v>
-      </c>
-      <c r="F19" s="4">
-        <v>8475.9599999999991</v>
-      </c>
-      <c r="G19" s="4">
-        <v>262193</v>
-      </c>
-      <c r="H19" s="4">
-        <v>68.679981822201199</v>
+        <v>0.9922239393087946</v>
       </c>
     </row>
   </sheetData>
@@ -19147,6 +20436,848 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0CB5E58-BD10-4113-A538-64E594317AC5}">
+  <dimension ref="A1:U19"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <cols>
+    <col min="1" max="1" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="12" max="15" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="19.6796875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:21" x14ac:dyDescent="0.75">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1">
+        <v>45727</v>
+      </c>
+      <c r="M1" s="1">
+        <v>45708</v>
+      </c>
+      <c r="N1" s="1">
+        <v>45638</v>
+      </c>
+      <c r="O1" s="1">
+        <v>45554</v>
+      </c>
+      <c r="P1" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>5</v>
+      </c>
+      <c r="R1" t="s">
+        <v>73</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.75">
+      <c r="A2" s="1">
+        <v>45554</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2">
+        <v>1.2</v>
+      </c>
+      <c r="E2">
+        <v>3.57</v>
+      </c>
+      <c r="F2">
+        <v>904.88</v>
+      </c>
+      <c r="G2">
+        <v>19268200</v>
+      </c>
+      <c r="H2">
+        <v>100.03049449091</v>
+      </c>
+      <c r="J2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L2">
+        <v>6.37</v>
+      </c>
+      <c r="M2">
+        <v>7.22</v>
+      </c>
+      <c r="P2">
+        <v>19864100</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.75">
+      <c r="A3" s="1">
+        <v>45554</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3">
+        <v>0.38</v>
+      </c>
+      <c r="E3">
+        <v>3.76</v>
+      </c>
+      <c r="F3">
+        <v>2002.8</v>
+      </c>
+      <c r="G3">
+        <v>5821280</v>
+      </c>
+      <c r="H3">
+        <v>100.03049449091</v>
+      </c>
+      <c r="J3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K3" t="s">
+        <v>9</v>
+      </c>
+      <c r="L3">
+        <v>3.77</v>
+      </c>
+      <c r="M3">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="N3">
+        <v>4.0599999999999996</v>
+      </c>
+      <c r="O3">
+        <v>1.2</v>
+      </c>
+      <c r="P3">
+        <v>19268200</v>
+      </c>
+      <c r="Q3">
+        <v>904.88</v>
+      </c>
+      <c r="R3">
+        <f>$P$2-P3</f>
+        <v>595900</v>
+      </c>
+      <c r="S3">
+        <f>R3/$P$2</f>
+        <v>2.9998842132288903E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.75">
+      <c r="A4" s="1">
+        <v>45554</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4">
+        <v>0.36</v>
+      </c>
+      <c r="E4">
+        <v>3.81</v>
+      </c>
+      <c r="F4">
+        <v>3140.96</v>
+      </c>
+      <c r="G4">
+        <v>1960760</v>
+      </c>
+      <c r="H4">
+        <v>100.03049449091</v>
+      </c>
+      <c r="J4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K4" t="s">
+        <v>8</v>
+      </c>
+      <c r="L4">
+        <v>3.04</v>
+      </c>
+      <c r="M4">
+        <v>3.16</v>
+      </c>
+      <c r="N4">
+        <v>3.7</v>
+      </c>
+      <c r="O4">
+        <v>0.38</v>
+      </c>
+      <c r="P4">
+        <v>5821280</v>
+      </c>
+      <c r="Q4">
+        <v>2002.8</v>
+      </c>
+      <c r="R4">
+        <f t="shared" ref="R4:R6" si="0">$P$2-P4</f>
+        <v>14042820</v>
+      </c>
+      <c r="S4">
+        <f t="shared" ref="S4:S6" si="1">R4/$P$2</f>
+        <v>0.70694468916286168</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.75">
+      <c r="A5" s="1">
+        <v>45554</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5">
+        <v>8475.9599999999991</v>
+      </c>
+      <c r="G5">
+        <v>262193</v>
+      </c>
+      <c r="H5">
+        <v>100.03049449091</v>
+      </c>
+      <c r="J5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K5" t="s">
+        <v>10</v>
+      </c>
+      <c r="L5">
+        <v>1.99</v>
+      </c>
+      <c r="M5">
+        <v>1.52</v>
+      </c>
+      <c r="N5">
+        <v>3.04</v>
+      </c>
+      <c r="O5">
+        <v>0.36</v>
+      </c>
+      <c r="P5">
+        <v>1960760</v>
+      </c>
+      <c r="Q5">
+        <v>3140.96</v>
+      </c>
+      <c r="R5">
+        <f t="shared" si="0"/>
+        <v>17903340</v>
+      </c>
+      <c r="S5">
+        <f t="shared" si="1"/>
+        <v>0.90129127420824506</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.75">
+      <c r="A6" s="3">
+        <v>45638</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="4">
+        <v>4.0599999999999996</v>
+      </c>
+      <c r="E6" s="4">
+        <v>3.6</v>
+      </c>
+      <c r="F6" s="4">
+        <v>904.88</v>
+      </c>
+      <c r="G6" s="4">
+        <v>19268200</v>
+      </c>
+      <c r="H6" s="4">
+        <v>5.30642319963549</v>
+      </c>
+      <c r="J6" t="s">
+        <v>16</v>
+      </c>
+      <c r="K6" t="s">
+        <v>11</v>
+      </c>
+      <c r="L6">
+        <v>8.9</v>
+      </c>
+      <c r="M6">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="N6">
+        <v>2.54</v>
+      </c>
+      <c r="P6">
+        <v>262193</v>
+      </c>
+      <c r="Q6">
+        <v>8475.9599999999991</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="0"/>
+        <v>19601907</v>
+      </c>
+      <c r="S6">
+        <f t="shared" si="1"/>
+        <v>0.98680066048801607</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.75">
+      <c r="A7" s="3">
+        <v>45638</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="4">
+        <v>3.7</v>
+      </c>
+      <c r="E7" s="4">
+        <v>4.0199999999999996</v>
+      </c>
+      <c r="F7" s="4">
+        <v>2002.8</v>
+      </c>
+      <c r="G7" s="4">
+        <v>5821280</v>
+      </c>
+      <c r="H7" s="4">
+        <v>5.30642319963549</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.75">
+      <c r="A8" s="3">
+        <v>45638</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="4">
+        <v>3.04</v>
+      </c>
+      <c r="E8" s="4">
+        <v>4.5199999999999996</v>
+      </c>
+      <c r="F8" s="4">
+        <v>3140.96</v>
+      </c>
+      <c r="G8" s="4">
+        <v>1960760</v>
+      </c>
+      <c r="H8" s="4">
+        <v>5.30642319963549</v>
+      </c>
+      <c r="J8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K8" t="s">
+        <v>26</v>
+      </c>
+      <c r="M8" t="s">
+        <v>21</v>
+      </c>
+      <c r="N8" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="P8" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R8" s="2"/>
+      <c r="T8" t="s">
+        <v>21</v>
+      </c>
+      <c r="U8" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.75">
+      <c r="A9" s="3">
+        <v>45638</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" s="4">
+        <v>2.54</v>
+      </c>
+      <c r="E9" s="4">
+        <v>4.5599999999999996</v>
+      </c>
+      <c r="F9" s="4">
+        <v>8475.9599999999991</v>
+      </c>
+      <c r="G9" s="4">
+        <v>262193</v>
+      </c>
+      <c r="H9" s="4">
+        <v>5.30642319963549</v>
+      </c>
+      <c r="I9" t="s">
+        <v>15</v>
+      </c>
+      <c r="J9">
+        <f>$S2*$H$2</f>
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <f>$S2*$H$6</f>
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <f>$S2*$H$10</f>
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>7.22</v>
+      </c>
+      <c r="T9">
+        <f>$S2*$H$15</f>
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>6.37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.75">
+      <c r="A10" s="1">
+        <v>45708</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10">
+        <v>7.22</v>
+      </c>
+      <c r="E10">
+        <v>3.71</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>19864100</v>
+      </c>
+      <c r="H10">
+        <v>37.743591811441398</v>
+      </c>
+      <c r="I10" t="s">
+        <v>9</v>
+      </c>
+      <c r="J10">
+        <f t="shared" ref="J10:J13" si="2">$S3*$H$2</f>
+        <v>3.0007990126476041</v>
+      </c>
+      <c r="K10">
+        <v>1.2</v>
+      </c>
+      <c r="M10">
+        <f t="shared" ref="M10:M13" si="3">$S3*$H$6</f>
+        <v>0.15918655185298042</v>
+      </c>
+      <c r="N10">
+        <v>4.0599999999999996</v>
+      </c>
+      <c r="P10">
+        <f t="shared" ref="P10:P12" si="4">$S3*$H$10</f>
+        <v>1.1322640522569827</v>
+      </c>
+      <c r="Q10">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="T10">
+        <f t="shared" ref="T10:T13" si="5">$S3*$H$15</f>
+        <v>2.0603199323326855</v>
+      </c>
+      <c r="U10">
+        <v>3.77</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.75">
+      <c r="A11" s="1">
+        <v>45708</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="E11">
+        <v>3.73</v>
+      </c>
+      <c r="F11">
+        <v>904.88</v>
+      </c>
+      <c r="G11">
+        <v>19268200</v>
+      </c>
+      <c r="H11">
+        <v>37.743591811441398</v>
+      </c>
+      <c r="I11" t="s">
+        <v>8</v>
+      </c>
+      <c r="J11">
+        <f t="shared" si="2"/>
+        <v>70.716026834683717</v>
+      </c>
+      <c r="K11">
+        <v>0.38</v>
+      </c>
+      <c r="M11">
+        <f t="shared" si="3"/>
+        <v>3.7513476994329094</v>
+      </c>
+      <c r="N11">
+        <v>3.7</v>
+      </c>
+      <c r="P11">
+        <f t="shared" si="4"/>
+        <v>26.682631781029372</v>
+      </c>
+      <c r="Q11">
+        <v>3.16</v>
+      </c>
+      <c r="T11">
+        <f t="shared" si="5"/>
+        <v>48.552948401007015</v>
+      </c>
+      <c r="U11">
+        <v>3.04</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.75">
+      <c r="A12" s="1">
+        <v>45708</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12">
+        <v>3.16</v>
+      </c>
+      <c r="E12">
+        <v>3.86</v>
+      </c>
+      <c r="F12">
+        <v>2002.8</v>
+      </c>
+      <c r="G12">
+        <v>5821280</v>
+      </c>
+      <c r="H12">
+        <v>37.743591811441398</v>
+      </c>
+      <c r="I12" t="s">
+        <v>10</v>
+      </c>
+      <c r="J12">
+        <f t="shared" si="2"/>
+        <v>90.156611839393108</v>
+      </c>
+      <c r="K12">
+        <v>0.36</v>
+      </c>
+      <c r="M12">
+        <f t="shared" si="3"/>
+        <v>4.782632927087664</v>
+      </c>
+      <c r="N12">
+        <v>3.04</v>
+      </c>
+      <c r="P12">
+        <f t="shared" si="4"/>
+        <v>34.017969956929903</v>
+      </c>
+      <c r="Q12">
+        <v>1.52</v>
+      </c>
+      <c r="T12">
+        <f t="shared" si="5"/>
+        <v>61.900668329130831</v>
+      </c>
+      <c r="U12">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.75">
+      <c r="A13" s="1">
+        <v>45708</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13">
+        <v>1.52</v>
+      </c>
+      <c r="E13">
+        <v>3.97</v>
+      </c>
+      <c r="F13">
+        <v>3140.96</v>
+      </c>
+      <c r="G13">
+        <v>1960760</v>
+      </c>
+      <c r="H13">
+        <v>37.743591811441398</v>
+      </c>
+      <c r="I13" t="s">
+        <v>11</v>
+      </c>
+      <c r="J13">
+        <f t="shared" si="2"/>
+        <v>98.710158032572849</v>
+      </c>
+      <c r="M13">
+        <f t="shared" si="3"/>
+        <v>5.2363819182292328</v>
+      </c>
+      <c r="N13">
+        <v>2.54</v>
+      </c>
+      <c r="P13">
+        <f>$S6*$H$10</f>
+        <v>37.245401328720448</v>
+      </c>
+      <c r="Q13">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="T13">
+        <f t="shared" si="5"/>
+        <v>67.773451424453086</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.75">
+      <c r="A14" s="1">
+        <v>45708</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="E14">
+        <v>5.44</v>
+      </c>
+      <c r="F14">
+        <v>8475.9599999999991</v>
+      </c>
+      <c r="G14">
+        <v>262193</v>
+      </c>
+      <c r="H14">
+        <v>37.743591811441398</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.75">
+      <c r="A15" s="3">
+        <v>45727</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" s="4">
+        <v>6.37</v>
+      </c>
+      <c r="E15" s="4">
+        <v>3.53</v>
+      </c>
+      <c r="F15" s="4">
+        <v>0</v>
+      </c>
+      <c r="G15" s="4">
+        <v>19864100</v>
+      </c>
+      <c r="H15" s="4">
+        <v>68.679981822201199</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.75">
+      <c r="A16" s="3">
+        <v>45727</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="4">
+        <v>3.77</v>
+      </c>
+      <c r="E16" s="4">
+        <v>3.54</v>
+      </c>
+      <c r="F16" s="4">
+        <v>904.88</v>
+      </c>
+      <c r="G16" s="4">
+        <v>19268200</v>
+      </c>
+      <c r="H16" s="4">
+        <v>68.679981822201199</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="A17" s="3">
+        <v>45727</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="4">
+        <v>3.04</v>
+      </c>
+      <c r="E17" s="4">
+        <v>3.72</v>
+      </c>
+      <c r="F17" s="4">
+        <v>2002.8</v>
+      </c>
+      <c r="G17" s="4">
+        <v>5821280</v>
+      </c>
+      <c r="H17" s="4">
+        <v>68.679981822201199</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="A18" s="3">
+        <v>45727</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" s="4">
+        <v>1.99</v>
+      </c>
+      <c r="E18" s="4">
+        <v>3.61</v>
+      </c>
+      <c r="F18" s="4">
+        <v>3140.96</v>
+      </c>
+      <c r="G18" s="4">
+        <v>1960760</v>
+      </c>
+      <c r="H18" s="4">
+        <v>68.679981822201199</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="A19" s="3">
+        <v>45727</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19" s="4">
+        <v>8.9</v>
+      </c>
+      <c r="E19" s="4">
+        <v>5.89</v>
+      </c>
+      <c r="F19" s="4">
+        <v>8475.9599999999991</v>
+      </c>
+      <c r="G19" s="4">
+        <v>262193</v>
+      </c>
+      <c r="H19" s="4">
+        <v>68.679981822201199</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85EC181A-D1D7-48D5-9F7D-DE1BA9F9A99E}">
   <dimension ref="A1:K30"/>
   <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
@@ -19501,7 +21632,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E204686C-8BC3-42B3-93C3-AC647B8FDF39}">
   <dimension ref="A1:P501"/>
   <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
@@ -39664,7 +41795,7 @@
         <v>4.49</v>
       </c>
       <c r="B450">
-        <f t="shared" ref="B450:B513" si="73">1.3543*A450+0.7943</f>
+        <f t="shared" ref="B450:B501" si="73">1.3543*A450+0.7943</f>
         <v>6.8751070000000007</v>
       </c>
       <c r="C450">
